--- a/data/raw/inventory/Week 28/Tonor/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 28/Tonor/Seller FBA Inventory (SP-API).xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,82 +417,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ASIN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>afn_fulfillable_quantity</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>afn_inbound_working_quantity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>afn_inbound_shipped_quantity</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>afn_inbound_receiving_quantity</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>afn_reserved_quantity</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>afn_total_quantity</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>afn_unsellable_quantity</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>afn_researching_quantity</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Seller Account</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
@@ -904,7 +892,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F8" t="n">
         <v>19</v>
@@ -919,10 +907,10 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1028,10 +1016,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F10" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1046,7 +1034,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1589,7 +1577,7 @@
         <v>17</v>
       </c>
       <c r="F19" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1601,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
         <v>18</v>
@@ -1648,13 +1636,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1666,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1834,13 +1822,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1852,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>

--- a/data/raw/inventory/Week 28/Tonor/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 28/Tonor/Seller FBA Inventory (SP-API).xlsx
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F10" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1034,7 +1034,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1450,25 +1450,25 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F17" t="n">
+        <v>17</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
         <v>19</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
         <v>14</v>
@@ -1589,10 +1589,10 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L19" t="n">
         <v>1</v>
@@ -1636,16 +1636,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1822,16 +1822,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
